--- a/results/cpp_johnson.xlsx
+++ b/results/cpp_johnson.xlsx
@@ -470,28 +470,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000756836</v>
+        <v>0.0007199881</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007324219999999</v>
+        <v>0.0007381166999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01070555</v>
+        <v>0.010027284</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0102905099999999</v>
+        <v>0.010794902</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08166503999999999</v>
+        <v>0.08148177999999991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08264161</v>
+        <v>0.07983535</v>
       </c>
       <c r="H2" t="n">
-        <v>10.20184</v>
+        <v>9.702108000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>10.12121</v>
+        <v>9.624864000000001</v>
       </c>
     </row>
     <row r="3">
@@ -499,28 +499,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005371093</v>
+        <v>0.0005282280000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005859376999999</v>
+        <v>0.0005684821</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005566404</v>
+        <v>0.006647066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005322263</v>
+        <v>0.0060971859999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0428467</v>
+        <v>0.042669</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04189452</v>
+        <v>0.0419889399999999</v>
       </c>
       <c r="H3" t="n">
-        <v>5.122901000000001</v>
+        <v>4.890283</v>
       </c>
       <c r="I3" t="n">
-        <v>5.073925999999998</v>
+        <v>4.848504</v>
       </c>
     </row>
     <row r="4">
@@ -528,28 +528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0005493165</v>
+        <v>0.0004963990999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0005249023</v>
+        <v>0.0005311552</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00415039</v>
+        <v>0.004847271</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004248046</v>
+        <v>0.004258412</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02980958</v>
+        <v>0.02781812</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03016357</v>
+        <v>0.0286425799999999</v>
       </c>
       <c r="H4" t="n">
-        <v>3.449366</v>
+        <v>3.267313</v>
       </c>
       <c r="I4" t="n">
-        <v>3.406421</v>
+        <v>3.395149</v>
       </c>
     </row>
     <row r="5">
@@ -557,28 +557,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0005981447999999</v>
+        <v>0.0005309132</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005615236</v>
+        <v>0.0005106600999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00341797</v>
+        <v>0.004088919</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003991699</v>
+        <v>0.003467227</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02248534</v>
+        <v>0.0235263699999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0236083999999999</v>
+        <v>0.02290905</v>
       </c>
       <c r="H5" t="n">
-        <v>2.587183</v>
+        <v>2.452249000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>2.654469</v>
+        <v>2.483608</v>
       </c>
     </row>
     <row r="6">
@@ -586,28 +586,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.000769043</v>
+        <v>0.0007979143</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000720215</v>
+        <v>0.0006625461999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0045166</v>
+        <v>0.004926141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0044311509999999</v>
+        <v>0.004302468</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0259155199999999</v>
+        <v>0.02670711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02635499</v>
+        <v>0.02617271</v>
       </c>
       <c r="H6" t="n">
-        <v>2.600097</v>
+        <v>2.517872</v>
       </c>
       <c r="I6" t="n">
-        <v>2.672511000000001</v>
+        <v>2.55022</v>
       </c>
     </row>
     <row r="7">
@@ -615,28 +615,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.000769043</v>
+        <v>0.0007271871</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0006835939999999</v>
+        <v>0.0007008076999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004052734</v>
+        <v>0.004683184</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004553221</v>
+        <v>0.0042505389999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02645262</v>
+        <v>0.0253889299999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02745361</v>
+        <v>0.02492111</v>
       </c>
       <c r="H7" t="n">
-        <v>2.769554</v>
+        <v>2.657986</v>
       </c>
       <c r="I7" t="n">
-        <v>2.805177</v>
+        <v>2.648109</v>
       </c>
     </row>
     <row r="8">
@@ -644,28 +644,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0008666987999999</v>
+        <v>0.0008055833999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007690427999999</v>
+        <v>0.0007398936</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003759766</v>
+        <v>0.004594401</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0043945299999999</v>
+        <v>0.004096304</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02485352</v>
+        <v>0.02415853</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02454834</v>
+        <v>0.02377593</v>
       </c>
       <c r="H8" t="n">
-        <v>2.648681</v>
+        <v>2.496451</v>
       </c>
       <c r="I8" t="n">
-        <v>2.607105</v>
+        <v>2.527101</v>
       </c>
     </row>
     <row r="9">
@@ -673,28 +673,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.000891113</v>
+        <v>0.0009314731</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009765615999998999</v>
+        <v>0.000797754</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0044311509999999</v>
+        <v>0.004560897</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00427246</v>
+        <v>0.004289404</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0233520599999999</v>
+        <v>0.02431792</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02454835</v>
+        <v>0.02717181</v>
       </c>
       <c r="H9" t="n">
-        <v>2.589306</v>
+        <v>2.475559</v>
       </c>
       <c r="I9" t="n">
-        <v>2.589039000000001</v>
+        <v>2.479117</v>
       </c>
     </row>
     <row r="10">
@@ -702,28 +702,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0009155268</v>
+        <v>0.0010580483</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009399405999999</v>
+        <v>0.0008665114</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004711914</v>
+        <v>0.0045824279999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004284667</v>
+        <v>0.004251701</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0255371</v>
+        <v>0.02459476</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02636719</v>
+        <v>0.02393817</v>
       </c>
       <c r="H10" t="n">
-        <v>2.630271</v>
+        <v>2.482504</v>
       </c>
       <c r="I10" t="n">
-        <v>2.584082</v>
+        <v>2.474484</v>
       </c>
     </row>
     <row r="11">
@@ -731,28 +731,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0011108373999999</v>
+        <v>0.0010520711</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001037596</v>
+        <v>0.0009241201</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00439453</v>
+        <v>0.004679767</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004711913</v>
+        <v>0.004514027</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0265014599999999</v>
+        <v>0.0262903699999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02735595</v>
+        <v>0.0258511</v>
       </c>
       <c r="H11" t="n">
-        <v>2.627345</v>
+        <v>2.522089</v>
       </c>
       <c r="I11" t="n">
-        <v>2.595898</v>
+        <v>2.535266</v>
       </c>
     </row>
     <row r="12">
@@ -760,28 +760,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0010620097999999</v>
+        <v>0.0011152362</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0011352512</v>
+        <v>0.0009372891</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004699705</v>
+        <v>0.004622746</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004504393</v>
+        <v>0.00469919</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0266967799999999</v>
+        <v>0.02713995</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02774658</v>
+        <v>0.02600289</v>
       </c>
       <c r="H12" t="n">
-        <v>2.611791</v>
+        <v>2.48261</v>
       </c>
       <c r="I12" t="n">
-        <v>2.525829</v>
+        <v>2.488294</v>
       </c>
     </row>
     <row r="13">
@@ -789,28 +789,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0012329072</v>
+        <v>0.001141572</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0012329072</v>
+        <v>0.0009354227</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004504393</v>
+        <v>0.005022646</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004772948</v>
+        <v>0.005006599</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0267944299999999</v>
+        <v>0.02866626</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0268921</v>
+        <v>0.02485525</v>
       </c>
       <c r="H13" t="n">
-        <v>2.565478</v>
+        <v>2.48707</v>
       </c>
       <c r="I13" t="n">
-        <v>2.509986</v>
+        <v>2.487018</v>
       </c>
     </row>
   </sheetData>
@@ -908,28 +908,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.40909122221492</v>
+        <v>1.363025246673785</v>
       </c>
       <c r="C3" t="n">
-        <v>1.249999786666782</v>
+        <v>1.29839919321998</v>
       </c>
       <c r="D3" t="n">
-        <v>1.923243444061912</v>
+        <v>1.508527822651377</v>
       </c>
       <c r="E3" t="n">
-        <v>1.933483933432057</v>
+        <v>1.770472804995645</v>
       </c>
       <c r="F3" t="n">
-        <v>1.905982024286584</v>
+        <v>1.909624786144506</v>
       </c>
       <c r="G3" t="n">
-        <v>1.972611453717575</v>
+        <v>1.901342353486423</v>
       </c>
       <c r="H3" t="n">
-        <v>1.991418534146961</v>
+        <v>1.983956347720572</v>
       </c>
       <c r="I3" t="n">
-        <v>1.994749233630921</v>
+        <v>1.985120358774583</v>
       </c>
     </row>
     <row r="4">
@@ -937,28 +937,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.377777656414836</v>
+        <v>1.45042184806569</v>
       </c>
       <c r="C4" t="n">
-        <v>1.395349191649379</v>
+        <v>1.389644119082332</v>
       </c>
       <c r="D4" t="n">
-        <v>2.579408200193234</v>
+        <v>2.068645223260676</v>
       </c>
       <c r="E4" t="n">
-        <v>2.42241020930562</v>
+        <v>2.534959510728413</v>
       </c>
       <c r="F4" t="n">
-        <v>2.739556880707477</v>
+        <v>2.929090103860358</v>
       </c>
       <c r="G4" t="n">
-        <v>2.739782127911252</v>
+        <v>2.787296046655025</v>
       </c>
       <c r="H4" t="n">
-        <v>2.957598584783407</v>
+        <v>2.969445535215022</v>
       </c>
       <c r="I4" t="n">
-        <v>2.971215243212744</v>
+        <v>2.834887069757469</v>
       </c>
     </row>
     <row r="5">
@@ -966,28 +966,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1.265305658429408</v>
+        <v>1.356131473092023</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3043476712286</v>
+        <v>1.445416824224176</v>
       </c>
       <c r="D5" t="n">
-        <v>3.132136911675643</v>
+        <v>2.452306832196969</v>
       </c>
       <c r="E5" t="n">
-        <v>2.577977447698311</v>
+        <v>3.11341080350378</v>
       </c>
       <c r="F5" t="n">
-        <v>3.631923733419196</v>
+        <v>3.463423384057985</v>
       </c>
       <c r="G5" t="n">
-        <v>3.500517188797223</v>
+        <v>3.484882611893553</v>
       </c>
       <c r="H5" t="n">
-        <v>3.943223189082489</v>
+        <v>3.956412256667246</v>
       </c>
       <c r="I5" t="n">
-        <v>3.81289440562312</v>
+        <v>3.875355531146622</v>
       </c>
     </row>
     <row r="6">
@@ -995,28 +995,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9841270254069019</v>
+        <v>0.9023376319988249</v>
       </c>
       <c r="C6" t="n">
-        <v>1.016949105475309</v>
+        <v>1.114060725123941</v>
       </c>
       <c r="D6" t="n">
-        <v>2.370267457822256</v>
+        <v>2.035525170716794</v>
       </c>
       <c r="E6" t="n">
-        <v>2.322310839779582</v>
+        <v>2.509002274973341</v>
       </c>
       <c r="F6" t="n">
-        <v>3.151202059615254</v>
+        <v>3.050939618700784</v>
       </c>
       <c r="G6" t="n">
-        <v>3.135710163426357</v>
+        <v>3.050327994311632</v>
       </c>
       <c r="H6" t="n">
-        <v>3.923638233496674</v>
+        <v>3.85329675217803</v>
       </c>
       <c r="I6" t="n">
-        <v>3.787153729208223</v>
+        <v>3.774130859298414</v>
       </c>
     </row>
     <row r="7">
@@ -1024,28 +1024,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9841270254069019</v>
+        <v>0.9901002094234069</v>
       </c>
       <c r="C7" t="n">
-        <v>1.071428362449066</v>
+        <v>1.053237143370578</v>
       </c>
       <c r="D7" t="n">
-        <v>2.641562461291563</v>
+        <v>2.141125354032641</v>
       </c>
       <c r="E7" t="n">
-        <v>2.260050632288637</v>
+        <v>2.539654853184562</v>
       </c>
       <c r="F7" t="n">
-        <v>3.087219337819845</v>
+        <v>3.209342812005084</v>
       </c>
       <c r="G7" t="n">
-        <v>3.010227434570536</v>
+        <v>3.203523037296493</v>
       </c>
       <c r="H7" t="n">
-        <v>3.683567823555706</v>
+        <v>3.650172724762283</v>
       </c>
       <c r="I7" t="n">
-        <v>3.608046836260242</v>
+        <v>3.634617759314288</v>
       </c>
     </row>
     <row r="8">
@@ -1053,28 +1053,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8732399306426722</v>
+        <v>0.8937474381921094</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9523813239003021</v>
+        <v>0.9975984384781811</v>
       </c>
       <c r="D8" t="n">
-        <v>2.847397949766023</v>
+        <v>2.182500830902657</v>
       </c>
       <c r="E8" t="n">
-        <v>2.341663386073172</v>
+        <v>2.635278534015054</v>
       </c>
       <c r="F8" t="n">
-        <v>3.28585407620329</v>
+        <v>3.372795447405116</v>
       </c>
       <c r="G8" t="n">
-        <v>3.366484658433116</v>
+        <v>3.357822385917186</v>
       </c>
       <c r="H8" t="n">
-        <v>3.851668056666696</v>
+        <v>3.8863602770493</v>
       </c>
       <c r="I8" t="n">
-        <v>3.882164316358566</v>
+        <v>3.808658221416556</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8493154066880406</v>
+        <v>0.7729564063632112</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7500008192007294</v>
+        <v>0.9252434961153437</v>
       </c>
       <c r="D9" t="n">
-        <v>2.415974991599303</v>
+        <v>2.198533314828201</v>
       </c>
       <c r="E9" t="n">
-        <v>2.408567897651447</v>
+        <v>2.516643804127566</v>
       </c>
       <c r="F9" t="n">
-        <v>3.497123594235384</v>
+        <v>3.350688710218633</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3664832870641</v>
+        <v>2.938168270718807</v>
       </c>
       <c r="H9" t="n">
-        <v>3.939990097732752</v>
+        <v>3.91915846077593</v>
       </c>
       <c r="I9" t="n">
-        <v>3.909253587914279</v>
+        <v>3.882375862050884</v>
       </c>
     </row>
     <row r="10">
@@ -1111,28 +1111,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8266672259075322</v>
+        <v>0.6804869872197706</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7792215805977292</v>
+        <v>0.8518257232391865</v>
       </c>
       <c r="D10" t="n">
-        <v>2.272017273659918</v>
+        <v>2.188203284372437</v>
       </c>
       <c r="E10" t="n">
-        <v>2.401705896864307</v>
+        <v>2.538960759470151</v>
       </c>
       <c r="F10" t="n">
-        <v>3.197897960222578</v>
+        <v>3.312973169894722</v>
       </c>
       <c r="G10" t="n">
-        <v>3.134259282085046</v>
+        <v>3.335064877557474</v>
       </c>
       <c r="H10" t="n">
-        <v>3.878626955169258</v>
+        <v>3.908194307038378</v>
       </c>
       <c r="I10" t="n">
-        <v>3.916752641750533</v>
+        <v>3.889644871415617</v>
       </c>
     </row>
     <row r="11">
@@ -1140,28 +1140,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6813202364271028</v>
+        <v>0.6843530822203937</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7058836001679845</v>
+        <v>0.798723780599513</v>
       </c>
       <c r="D11" t="n">
-        <v>2.436108070715185</v>
+        <v>2.142688727878973</v>
       </c>
       <c r="E11" t="n">
-        <v>2.183934635465447</v>
+        <v>2.391412811664618</v>
       </c>
       <c r="F11" t="n">
-        <v>3.081529847789529</v>
+        <v>3.099301379174208</v>
       </c>
       <c r="G11" t="n">
-        <v>3.02097386491787</v>
+        <v>3.088276707760985</v>
       </c>
       <c r="H11" t="n">
-        <v>3.882946472579734</v>
+        <v>3.846853937351141</v>
       </c>
       <c r="I11" t="n">
-        <v>3.898924379925559</v>
+        <v>3.796392173444522</v>
       </c>
     </row>
     <row r="12">
@@ -1169,28 +1169,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7126450245563377</v>
+        <v>0.6455924762843961</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6451629383874687</v>
+        <v>0.7875016363681173</v>
       </c>
       <c r="D12" t="n">
-        <v>2.277919571547576</v>
+        <v>2.16911852825139</v>
       </c>
       <c r="E12" t="n">
-        <v>2.284549771745028</v>
+        <v>2.297183557166235</v>
       </c>
       <c r="F12" t="n">
-        <v>3.058984641593492</v>
+        <v>3.002281875979871</v>
       </c>
       <c r="G12" t="n">
-        <v>2.978443109024608</v>
+        <v>3.070249114617644</v>
       </c>
       <c r="H12" t="n">
-        <v>3.906070585280369</v>
+        <v>3.908027438864743</v>
       </c>
       <c r="I12" t="n">
-        <v>4.007084406743291</v>
+        <v>3.868057391931983</v>
       </c>
     </row>
     <row r="13">
@@ -1198,28 +1198,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6138629087412256</v>
+        <v>0.6306988083099445</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5940609317553665</v>
+        <v>0.789072897204654</v>
       </c>
       <c r="D13" t="n">
-        <v>2.376690932607346</v>
+        <v>1.996414638817866</v>
       </c>
       <c r="E13" t="n">
-        <v>2.15600714694564</v>
+        <v>2.156134733378887</v>
       </c>
       <c r="F13" t="n">
-        <v>3.047836434661991</v>
+        <v>2.842427997234376</v>
       </c>
       <c r="G13" t="n">
-        <v>3.073081313843099</v>
+        <v>3.212011546856298</v>
       </c>
       <c r="H13" t="n">
-        <v>3.976584480552942</v>
+        <v>3.901019271673094</v>
       </c>
       <c r="I13" t="n">
-        <v>4.03237707301953</v>
+        <v>3.870041953857994</v>
       </c>
     </row>
   </sheetData>
@@ -1317,28 +1317,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7045456111074598</v>
+        <v>0.6815126233368923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6249998933333911</v>
+        <v>0.64919959660999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9616217220309558</v>
+        <v>0.7542639113256886</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9667419667160285</v>
+        <v>0.8852364024978225</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9529910121432922</v>
+        <v>0.9548123930722529</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9863057268587874</v>
+        <v>0.9506711767432113</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9957092670734804</v>
+        <v>0.9919781738602859</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9973746168154604</v>
+        <v>0.9925601793872915</v>
       </c>
     </row>
     <row r="4">
@@ -1346,28 +1346,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4592592188049452</v>
+        <v>0.4834739493552299</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4651163972164598</v>
+        <v>0.4632147063607774</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8598027333977448</v>
+        <v>0.6895484077535586</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8074700697685399</v>
+        <v>0.8449865035761376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9131856269024924</v>
+        <v>0.9763633679534527</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9132607093037506</v>
+        <v>0.9290986822183416</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9858661949278024</v>
+        <v>0.9898151784050074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9904050810709147</v>
+        <v>0.9449623565858229</v>
       </c>
     </row>
     <row r="5">
@@ -1375,28 +1375,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.316326414607352</v>
+        <v>0.3390328682730058</v>
       </c>
       <c r="C5" t="n">
-        <v>0.32608691780715</v>
+        <v>0.361354206056044</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7830342279189109</v>
+        <v>0.6130767080492423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6444943619245778</v>
+        <v>0.778352700875945</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9079809333547991</v>
+        <v>0.8658558460144962</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8751292971993057</v>
+        <v>0.8712206529733882</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9858057972706222</v>
+        <v>0.9891030641668115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9532236014057801</v>
+        <v>0.9688388827866555</v>
       </c>
     </row>
     <row r="6">
@@ -1404,28 +1404,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1968254050813804</v>
+        <v>0.180467526399765</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2033898210950619</v>
+        <v>0.2228121450247881</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4740534915644511</v>
+        <v>0.4071050341433589</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4644621679559163</v>
+        <v>0.5018004549946682</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6302404119230508</v>
+        <v>0.6101879237401568</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6271420326852715</v>
+        <v>0.6100655988623265</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7847276466993348</v>
+        <v>0.770659350435606</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7574307458416446</v>
+        <v>0.7548261718596827</v>
       </c>
     </row>
     <row r="7">
@@ -1433,28 +1433,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1640211709011503</v>
+        <v>0.1650167015705678</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1785713937415111</v>
+        <v>0.1755395238950964</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4402604102152605</v>
+        <v>0.3568542256721068</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3766751053814395</v>
+        <v>0.4232758088640937</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5145365563033075</v>
+        <v>0.5348904686675139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5017045724284226</v>
+        <v>0.5339205062160821</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6139279705926177</v>
+        <v>0.6083621207937138</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6013411393767071</v>
+        <v>0.6057696265523813</v>
       </c>
     </row>
     <row r="8">
@@ -1462,28 +1462,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1247485615203817</v>
+        <v>0.1276782054560156</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1360544748429003</v>
+        <v>0.1425140626397401</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4067711356808604</v>
+        <v>0.3117858329860939</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3345233408675959</v>
+        <v>0.3764683620021505</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4694077251718985</v>
+        <v>0.4818279210578736</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4809263797761595</v>
+        <v>0.4796889122738837</v>
       </c>
       <c r="H8" t="n">
-        <v>0.550238293809528</v>
+        <v>0.5551943252927571</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5545949023369381</v>
+        <v>0.5440940316309365</v>
       </c>
     </row>
     <row r="9">
@@ -1491,28 +1491,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1061644258360051</v>
+        <v>0.0966195507954014</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09375010240009117</v>
+        <v>0.115655437014418</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3019968739499128</v>
+        <v>0.2748166643535251</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3010709872064309</v>
+        <v>0.3145804755159458</v>
       </c>
       <c r="F9" t="n">
-        <v>0.437140449279423</v>
+        <v>0.4188360887773291</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4208104108830125</v>
+        <v>0.3672710338398509</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4924987622165939</v>
+        <v>0.4898948075969913</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4886566984892849</v>
+        <v>0.4852969827563605</v>
       </c>
     </row>
     <row r="10">
@@ -1520,28 +1520,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.09185191398972579</v>
+        <v>0.07560966524664119</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0865801756219699</v>
+        <v>0.09464730258213183</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2524463637399909</v>
+        <v>0.2431336982636041</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2668562107627008</v>
+        <v>0.282106751052239</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3553219955802864</v>
+        <v>0.3681081299883024</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3482510313427829</v>
+        <v>0.3705627641730527</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4309585505743621</v>
+        <v>0.4342438118931531</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4351947379722814</v>
+        <v>0.4321827634906241</v>
       </c>
     </row>
     <row r="11">
@@ -1549,28 +1549,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06813202364271029</v>
+        <v>0.06843530822203937</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07058836001679844</v>
+        <v>0.0798723780599513</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2436108070715185</v>
+        <v>0.2142688727878973</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2183934635465447</v>
+        <v>0.2391412811664618</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3081529847789529</v>
+        <v>0.3099301379174207</v>
       </c>
       <c r="G11" t="n">
-        <v>0.302097386491787</v>
+        <v>0.3088276707760985</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3882946472579734</v>
+        <v>0.3846853937351141</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3898924379925559</v>
+        <v>0.3796392173444522</v>
       </c>
     </row>
     <row r="12">
@@ -1578,28 +1578,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.06478591132330343</v>
+        <v>0.05869022511676328</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05865117621704261</v>
+        <v>0.07159105785164703</v>
       </c>
       <c r="D12" t="n">
-        <v>0.207083597413416</v>
+        <v>0.1971925934773991</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2076863428859116</v>
+        <v>0.2088348688332941</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2780895128721356</v>
+        <v>0.2729347159981701</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2707675553658734</v>
+        <v>0.2791135558743313</v>
       </c>
       <c r="H12" t="n">
-        <v>0.355097325934579</v>
+        <v>0.3552752217149767</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3642804006130265</v>
+        <v>0.3516415810847257</v>
       </c>
     </row>
     <row r="13">
@@ -1607,28 +1607,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05115524239510214</v>
+        <v>0.05255823402582871</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04950507764628054</v>
+        <v>0.0657560747670545</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1980575777172788</v>
+        <v>0.1663678865681555</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17966726224547</v>
+        <v>0.1796778944482406</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2539863695551659</v>
+        <v>0.2368689997695314</v>
       </c>
       <c r="G13" t="n">
-        <v>0.256090109486925</v>
+        <v>0.2676676289046915</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3313820400460785</v>
+        <v>0.3250849393060911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3360314227516275</v>
+        <v>0.3225034961548328</v>
       </c>
     </row>
   </sheetData>
